--- a/docs/acceptance-tests.xlsx
+++ b/docs/acceptance-tests.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6368a6be5aca3f60/Documents/HTL/WMC/room-food/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ostap\School_Files\Year_3\room-food\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{44113145-4501-44D9-A1EB-8D4ED0044DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37085657-5CE5-435C-AD87-8C2E7698B10D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0B958E-CEE2-464C-87FA-AFAE74E873D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D6859AF-9A25-468C-BEF1-C20AEB03BB66}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{8D6859AF-9A25-468C-BEF1-C20AEB03BB66}"/>
   </bookViews>
   <sheets>
     <sheet name="All Tests" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sprint 2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -172,13 +173,127 @@
   </si>
   <si>
     <t>satisfy criteria of #14, when creating a meal, a user should be able to choose from saved or public recipes or create a new recipe, a recipe should contain a list of ingredients, steps of preparation (description) and time to prepare, a recipe should be either private or public, a recipe should be able to be shared per link</t>
+  </si>
+  <si>
+    <t>Login hashing and salting</t>
+  </si>
+  <si>
+    <t>Cookies for account</t>
+  </si>
+  <si>
+    <t>Add possibility to delete your account</t>
+  </si>
+  <si>
+    <t>Add a log out button</t>
+  </si>
+  <si>
+    <t>Adding new properties to user</t>
+  </si>
+  <si>
+    <t>Adding profile page</t>
+  </si>
+  <si>
+    <t>Add functionality for editing an existing meal</t>
+  </si>
+  <si>
+    <t>Calendar design for room view</t>
+  </si>
+  <si>
+    <t>Room backend</t>
+  </si>
+  <si>
+    <t>Create room frontend</t>
+  </si>
+  <si>
+    <t>Edit room frontend</t>
+  </si>
+  <si>
+    <t>Delete room frontend</t>
+  </si>
+  <si>
+    <t>Room overview</t>
+  </si>
+  <si>
+    <t>Invite functionality</t>
+  </si>
+  <si>
+    <t>Control access to pages if not logged in</t>
+  </si>
+  <si>
+    <t>Add error page</t>
+  </si>
+  <si>
+    <t>Login and sign up</t>
+  </si>
+  <si>
+    <t>Profile functionality</t>
+  </si>
+  <si>
+    <t>Miscellaneous</t>
+  </si>
+  <si>
+    <t>The user should the means to customize their profile. Including, first name, last name, DOB and profile picture. All the changes should be visible and persistent.</t>
+  </si>
+  <si>
+    <t>The users should be able to edits meals they have access to.</t>
+  </si>
+  <si>
+    <t>Instead of storing the meal plans as boxes makes them sorted and presented in a calendar-like way (Similar to "WebUntis").</t>
+  </si>
+  <si>
+    <t>When logging in website should request to use cookies and if accepted use them to temporarily save the login data.</t>
+  </si>
+  <si>
+    <t>Appropriate button exists in the the individual room view from #95 to invite users using their usernames, after which the invitied user will have a way to accept or decline the invitation.</t>
+  </si>
+  <si>
+    <t>A webpage exists and accessible that shows a user all the rooms he has access to. Clicking on any of the rooms opens the webpage for that room where he can see the meal plans.</t>
+  </si>
+  <si>
+    <t>Appropriate button exists in the room overview(#95) to delete an existing room user has the appropriate rights for. Such a button should also exist in the individual room overview.</t>
+  </si>
+  <si>
+    <t>Appropriate button exists in the room overview(#95) to edit properties of an existing room user has editing rights for. Such a button should also exist in the individual room overview.</t>
+  </si>
+  <si>
+    <t>Appropriate button exists in the room overview(#95) to create a new room.</t>
+  </si>
+  <si>
+    <t>There exists an appropriate service and database to make  tasks #92, #93, #94 and #95 possible.</t>
+  </si>
+  <si>
+    <t>If the user requests to delete his account and completely remove it from the database.</t>
+  </si>
+  <si>
+    <t>logout button which logs a user out of his account .</t>
+  </si>
+  <si>
+    <t>When the user signs up the password gets hashed and salted before getting added to the database, password stored in the database should not be readable without the method to decrypt them.</t>
+  </si>
+  <si>
+    <t>Make corresponding changes in the database structure to make #85 possible.</t>
+  </si>
+  <si>
+    <t>satisfy criteria of #86 and #96.</t>
+  </si>
+  <si>
+    <t>If the entered route doesn't exist redirect the user to an error page which has to have a link to the homepage and notify user that the specified route doesn't exist.</t>
+  </si>
+  <si>
+    <t>User should not be able to access any page except the homepage, login page and sign up page.</t>
+  </si>
+  <si>
+    <t>satisfy criteria of #78, #79, #80 and #81.</t>
+  </si>
+  <si>
+    <t>satisfy criteria of #84 and #85.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +308,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Inherit"/>
     </font>
   </fonts>
   <fills count="2">
@@ -215,9 +342,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,14 +691,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="254.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +709,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>4</v>
       </c>
@@ -585,7 +720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -596,7 +731,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>6</v>
       </c>
@@ -607,7 +742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>7</v>
       </c>
@@ -618,7 +753,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>8</v>
       </c>
@@ -629,7 +764,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>10</v>
       </c>
@@ -640,7 +775,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>11</v>
       </c>
@@ -651,7 +786,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>12</v>
       </c>
@@ -662,7 +797,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>13</v>
       </c>
@@ -673,7 +808,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>14</v>
       </c>
@@ -684,7 +819,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>16</v>
       </c>
@@ -695,7 +830,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>22</v>
       </c>
@@ -721,14 +856,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="140.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +874,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -750,7 +885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>3</v>
       </c>
@@ -761,7 +896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>9</v>
       </c>
@@ -772,7 +907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>15</v>
       </c>
@@ -783,7 +918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>17</v>
       </c>
@@ -794,7 +929,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>18</v>
       </c>
@@ -805,7 +940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>19</v>
       </c>
@@ -816,7 +951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>20</v>
       </c>
@@ -827,7 +962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>21</v>
       </c>
@@ -842,4 +977,246 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C39D4E-7CC2-4A35-8234-C02BD352D8BB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.6640625" customWidth="1"/>
+    <col min="3" max="3" width="156.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>79</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>80</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>94</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C20">
+    <sortCondition ref="A3:A20"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/acceptance-tests.xlsx
+++ b/docs/acceptance-tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ostap\School_Files\Year_3\room-food\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Documents\HTL\3IHIF\WMC\room-food-docs\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0B958E-CEE2-464C-87FA-AFAE74E873D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E65FBFC-9B83-4504-9054-7875ABA082B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{8D6859AF-9A25-468C-BEF1-C20AEB03BB66}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{8D6859AF-9A25-468C-BEF1-C20AEB03BB66}"/>
   </bookViews>
   <sheets>
     <sheet name="All Tests" sheetId="1" r:id="rId1"/>
@@ -232,9 +232,6 @@
     <t>Miscellaneous</t>
   </si>
   <si>
-    <t>The user should the means to customize their profile. Including, first name, last name, DOB and profile picture. All the changes should be visible and persistent.</t>
-  </si>
-  <si>
     <t>The users should be able to edits meals they have access to.</t>
   </si>
   <si>
@@ -265,9 +262,6 @@
     <t>If the user requests to delete his account and completely remove it from the database.</t>
   </si>
   <si>
-    <t>logout button which logs a user out of his account .</t>
-  </si>
-  <si>
     <t>When the user signs up the password gets hashed and salted before getting added to the database, password stored in the database should not be readable without the method to decrypt them.</t>
   </si>
   <si>
@@ -287,6 +281,12 @@
   </si>
   <si>
     <t>satisfy criteria of #84 and #85.</t>
+  </si>
+  <si>
+    <t>The user should have the means to customize their profile. Including, first name, last name, DOB and profile picture. All the changes should be visible and persistent.</t>
+  </si>
+  <si>
+    <t>Logout button which logs a user out of their account.</t>
   </si>
 </sst>
 </file>
@@ -342,17 +342,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1011,7 +1010,7 @@
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1022,7 +1021,7 @@
         <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1033,7 +1032,7 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1044,7 +1043,7 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1055,7 +1054,7 @@
         <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1066,7 +1065,7 @@
         <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1077,7 +1076,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1088,7 +1087,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1099,7 +1098,7 @@
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1109,8 +1108,8 @@
       <c r="B11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>65</v>
+      <c r="C11" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1121,7 +1120,7 @@
         <v>49</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1132,7 +1131,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1143,7 +1142,7 @@
         <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1154,7 +1153,7 @@
         <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1165,7 +1164,7 @@
         <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1176,7 +1175,7 @@
         <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1187,7 +1186,7 @@
         <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1198,7 +1197,7 @@
         <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1209,7 +1208,7 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
